--- a/MEME_OUTPUT/reverse_meme_out_3_motif8.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_3_motif8.xlsx
@@ -477,16 +477,16 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TAT</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>ATA</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>TAT</t>
-        </is>
-      </c>
       <c r="G2" t="n">
-        <v>0.1596</v>
+        <v>0.1597361055577769</v>
       </c>
     </row>
     <row r="3">
@@ -511,11 +511,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.608</v>
+        <v>0.6079568172730908</v>
       </c>
     </row>
     <row r="4">
@@ -540,11 +540,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.9804</v>
+        <v>0.9802079168332667</v>
       </c>
     </row>
     <row r="5">
@@ -569,11 +569,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.3634</v>
+        <v>0.3634546181527389</v>
       </c>
     </row>
     <row r="6">
@@ -598,11 +598,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.8314</v>
+        <v>0.8312674930027989</v>
       </c>
     </row>
     <row r="7">
@@ -627,11 +627,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0.9562</v>
+        <v>0.9560175929628149</v>
       </c>
     </row>
     <row r="8">
@@ -656,11 +656,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.4834</v>
+        <v>0.483406637345062</v>
       </c>
     </row>
     <row r="9">
@@ -685,11 +685,11 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>TA</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.7524</v>
+        <v>0.7522990803678529</v>
       </c>
     </row>
   </sheetData>

--- a/MEME_OUTPUT/reverse_meme_out_3_motif8.xlsx
+++ b/MEME_OUTPUT/reverse_meme_out_3_motif8.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,15 +446,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>full_pattern</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>group1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>group2</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>full_pattern_html</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
@@ -477,15 +487,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>TATATA</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>TAT</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>ATA</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>0.1597361055577769</v>
       </c>
     </row>
@@ -506,7 +526,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>TAGTGATTTA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -514,7 +534,17 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;GTGATT&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>0.6079568172730908</v>
       </c>
     </row>
@@ -535,15 +565,25 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>ATTTAT</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;TT&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>0.9802079168332667</v>
       </c>
     </row>
@@ -564,7 +604,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>TAGTGATTTATA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -572,7 +612,17 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;GTGATTTA&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>0.3634546181527389</v>
       </c>
     </row>
@@ -593,7 +643,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>TATA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -601,7 +651,17 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>0.8312674930027989</v>
       </c>
     </row>
@@ -622,15 +682,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>ATTTATAT</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>AT</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;TTAT&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>0.9560175929628149</v>
       </c>
     </row>
@@ -651,7 +721,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>TAGTGATTTATATA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -659,7 +729,17 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;GTGATTTATA&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>0.483406637345062</v>
       </c>
     </row>
@@ -680,7 +760,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>TATA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -688,7 +768,17 @@
           <t>TA</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>&lt;span style="color: blue; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: blue; font-weight: bold;"&gt;A&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;T&lt;/span&gt;&lt;span style="color: red; font-weight: bold;"&gt;A&lt;/span&gt;</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>0.7522990803678529</v>
       </c>
     </row>
